--- a/examples/STUDY01_TRAIL01/outputs/reports/MW_issues.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/MW_issues.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -83,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,7 +95,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 14:31</t>
+          <t>Last run: 23Apr2026 17:08</t>
         </is>
       </c>
     </row>
@@ -549,10 +557,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -587,14 +595,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -612,7 +620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 14:31</t>
+          <t>Last run: 23Apr2026 17:08</t>
         </is>
       </c>
     </row>
@@ -671,24 +679,24 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK004</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-002</t>
+          <t>SUBJ-001</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v/>
+        <v>400</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: RASH starting 2023-04-29 (AESEQ=6)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v/>
+          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 10MG at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>46135</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -701,58 +709,58 @@
       <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>AEPRJ003</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>SUBJ-003</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>AE study day (AESTDY) is missing for term: FATIGUE starting 2023-04-10 (AESEQ=14)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>ECCHK004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>SUBJ-004</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK004</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-006</t>
+          <t>SUBJ-007</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v/>
+        <v>500</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: INSOMNIA starting 2022-12-21 (AESEQ=25)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v/>
+          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>46135</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -765,117 +773,105 @@
       <c r="J6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>AEPRJ003</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>SUBJ-010</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>AE study day (AESTDY) is missing for term: NAUSEA starting 2023-03-16 (AESEQ=39)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ECCHK005</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>SUBJ-002</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Administration status (ECSTAT) is missing for treatment: PLACEBO at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>ECCHK005</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-001</t>
+          <t>SUBJ-005</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (TABLET/CAPSULE) for treatment: DRUG A 10MG at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
+          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>ganesh</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>ganesh</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>ganesh</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>ganesh</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>ECCHK004</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>SUBJ-004</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>ECCHK005</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>SUBJ-009</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Dose form 'INJECTION' not in allowed list (TABLET/CAPSULE) for treatment: DRUG A 20MG at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -884,14 +880,16 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>400</v>
+        <v/>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: PLACEBO at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
+          <t>AE study day (AESTDY) is missing for term: RASH starting 2023-04-29 (AESEQ=6)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -903,63 +901,59 @@
       <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ECCHK005</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>SUBJ-005</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>AEPRJ003</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>SUBJ-003</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>AE study day (AESTDY) is missing for term: FATIGUE starting 2023-04-10 (AESEQ=14)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>OTTA</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>OTTA</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-009</t>
+          <t>SUBJ-006</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>300</v>
+        <v/>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
+          <t>AE study day (AESTDY) is missing for term: INSOMNIA starting 2022-12-21 (AESEQ=25)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -970,6 +964,38 @@
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>AEPRJ003</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>SUBJ-010</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>AE study day (AESTDY) is missing for term: NAUSEA starting 2023-03-16 (AESEQ=39)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/STUDY01_TRAIL01/outputs/reports/MW_issues.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/MW_issues.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 17:08</t>
+          <t>Last run: 23Apr2026 18:07</t>
         </is>
       </c>
     </row>
@@ -557,10 +557,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -578,10 +578,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -603,9 +603,9 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
@@ -620,7 +620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 17:08</t>
+          <t>Last run: 23Apr2026 18:07</t>
         </is>
       </c>
     </row>
@@ -679,20 +679,20 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-001</t>
+          <t>SUBJ-002</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>400</v>
+        <v/>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 10MG at visit WEEK 8</t>
+          <t>AE study day (AESTDY) is missing for term: RASH starting 2023-04-29 (AESEQ=6)</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
@@ -700,31 +700,47 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
+          <t>queried</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>chetan</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>chetan</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>chetan</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>chetan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-004</t>
+          <t>SUBJ-003</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>300</v>
+        <v/>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit WEEK 4</t>
+          <t>AE study day (AESTDY) is missing for term: FATIGUE starting 2023-04-10 (AESEQ=14)</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
@@ -737,26 +753,30 @@
       </c>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-007</t>
+          <t>SUBJ-006</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>500</v>
+        <v/>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
+          <t>AE study day (AESTDY) is missing for term: INSOMNIA starting 2022-12-21 (AESEQ=25)</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -768,27 +788,31 @@
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-002</t>
+          <t>SUBJ-010</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>400</v>
+        <v/>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: PLACEBO at visit WEEK 8</t>
+          <t>AE study day (AESTDY) is missing for term: NAUSEA starting 2023-03-16 (AESEQ=39)</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -799,7 +823,11 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
@@ -807,20 +835,20 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>ECCHK004</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-005</t>
+          <t>SUBJ-001</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit END OF TREATMENT</t>
+          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 10MG at visit WEEK 8</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -828,23 +856,39 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
+          <t>queried</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>ganesh</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>ganesh</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>ganesh</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>ganesh</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>ECCHK004</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-009</t>
+          <t>SUBJ-004</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -852,7 +896,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit WEEK 4</t>
+          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit WEEK 4</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -863,15 +907,23 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>whY?</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK005</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -880,11 +932,11 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v/>
+        <v>400</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: RASH starting 2023-04-29 (AESEQ=6)</t>
+          <t>Administration status (ECSTAT) is missing for treatment: PLACEBO at visit WEEK 8</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -895,28 +947,36 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK005</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-003</t>
+          <t>SUBJ-009</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: FATIGUE starting 2023-04-10 (AESEQ=14)</t>
+          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit WEEK 4</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -929,72 +989,12 @@
       </c>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="J11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>AEPRJ003</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>SUBJ-006</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>AE study day (AESTDY) is missing for term: INSOMNIA starting 2022-12-21 (AESEQ=25)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>46135</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>AEPRJ003</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>SUBJ-010</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>AE study day (AESTDY) is missing for term: NAUSEA starting 2023-03-16 (AESEQ=39)</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>46135</v>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/STUDY01_TRAIL01/outputs/reports/MW_issues.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/MW_issues.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 18:07</t>
+          <t>Last run: 23Apr2026 21:48</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 18:07</t>
+          <t>Last run: 23Apr2026 21:48</t>
         </is>
       </c>
     </row>
@@ -679,20 +679,20 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK004</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-002</t>
+          <t>SUBJ-001</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v/>
+        <v>400</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: RASH starting 2023-04-29 (AESEQ=6)</t>
+          <t>Dose form 'INJECTION' not in allowed list (TABLET/CAPSULE) for treatment: DRUG A 10MG at visit WEEK 8</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
@@ -705,42 +705,42 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>chetan</t>
+          <t>ganesh</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>chetan</t>
+          <t>ganesh</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>chetan</t>
+          <t>ganesh</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>chetan</t>
+          <t>ganesh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK004</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-003</t>
+          <t>SUBJ-004</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: FATIGUE starting 2023-04-10 (AESEQ=14)</t>
+          <t>Dose form 'INJECTION' not in allowed list (TABLET/CAPSULE) for treatment: DRUG A 20MG at visit WEEK 4</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
@@ -751,32 +751,36 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>whY?</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>not so good</t>
         </is>
       </c>
+      <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK005</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-006</t>
+          <t>SUBJ-002</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v/>
+        <v>400</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: INSOMNIA starting 2022-12-21 (AESEQ=25)</t>
+          <t>Administration status (ECSTAT) is missing for treatment: PLACEBO at visit WEEK 8</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -787,32 +791,36 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>not so good</t>
         </is>
       </c>
+      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>AEPRJ003</t>
+          <t>ECCHK005</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-010</t>
+          <t>SUBJ-009</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>AE study day (AESTDY) is missing for term: NAUSEA starting 2023-03-16 (AESEQ=39)</t>
+          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit WEEK 4</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -823,32 +831,32 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>not so good</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-001</t>
+          <t>SUBJ-002</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>400</v>
+        <v/>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 10MG at visit WEEK 8</t>
+          <t>AE study day (AESTDY) is missing for term: RASH starting 2023-04-29 (AESEQ=6)</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -861,42 +869,42 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>ganesh</t>
+          <t>chetan</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>ganesh</t>
+          <t>chetan</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>ganesh</t>
+          <t>chetan</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>ganesh</t>
+          <t>chetan</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-004</t>
+          <t>SUBJ-003</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>300</v>
+        <v/>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit WEEK 4</t>
+          <t>AE study day (AESTDY) is missing for term: FATIGUE starting 2023-04-10 (AESEQ=14)</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -907,36 +915,32 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>whY?</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>not so good</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>SUBJ-002</t>
+          <t>SUBJ-006</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>400</v>
+        <v/>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: PLACEBO at visit WEEK 8</t>
+          <t>AE study day (AESTDY) is missing for term: INSOMNIA starting 2022-12-21 (AESEQ=25)</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -947,36 +951,32 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>not so good</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>not so good</t>
-        </is>
-      </c>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ECCHK005</t>
+          <t>AEPRJ003</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SUBJ-009</t>
+          <t>SUBJ-010</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>300</v>
+        <v/>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit WEEK 4</t>
+          <t>AE study day (AESTDY) is missing for term: NAUSEA starting 2023-03-16 (AESEQ=39)</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -987,13 +987,13 @@
           <t>open</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>not so good</t>
+        </is>
+      </c>
       <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>not so good</t>
-        </is>
-      </c>
+      <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
